--- a/Assets/outputs/region_link_setup/zombie_card_design_template_v1_linked.xlsx
+++ b/Assets/outputs/region_link_setup/zombie_card_design_template_v1_linked.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\water\Desktop\GameDev\Zombie_cardSurvive\Assets\outputs\region_link_setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33F1DA29-9810-4692-B70D-45661EE3899A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35FCE73A-D840-46FA-8445-E94F46D8267A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1231" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="660">
   <si>
     <t>Zombie Card Survive - 第一版卡牌設計討論基板</t>
   </si>
@@ -2592,34 +2592,65 @@
     <t>當前機率</t>
   </si>
   <si>
+    <t>PACK-RARE-RESOURCE-01</t>
+  </si>
+  <si>
+    <t>PACK-STOREHOUSE-01</t>
+  </si>
+  <si>
+    <t>罕見資源包</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜索住宅</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>PACK-COMMON-FOOD-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡易食物包</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACK-COMMON-RESOURCE-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACK-UNCOMMON-RESOURCE-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>PACK-REGION-002-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>PACK-UNCOMMON-FOOD-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>PACK-RARE-SUPPLY-01</t>
-  </si>
-  <si>
-    <t>PACK-COMMON-RESOURCE-01</t>
-  </si>
-  <si>
-    <t>PACK-UNCOMMON-RESOURCE-01</t>
-  </si>
-  <si>
-    <t>PACK-REGION-002-01</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>食物補給</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>資源補給</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draft</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Food</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>PACK-FireDepartment-01</t>
-  </si>
-  <si>
-    <t>PACK-RARE-RESOURCE-01</t>
-  </si>
-  <si>
-    <t>PACK-STOREHOUSE-01</t>
-  </si>
-  <si>
-    <t>罕見資源包</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -2629,7 +2660,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="178" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -2999,7 +3030,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -5310,20 +5341,42 @@
     </row>
     <row r="28" spans="1:24" ht="38.1" customHeight="1">
       <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="B28" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="H28" s="5"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
+      <c r="I28" s="4">
+        <v>3</v>
+      </c>
+      <c r="J28" s="4">
+        <v>2</v>
+      </c>
       <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
+      <c r="L28" s="4">
+        <v>0</v>
+      </c>
+      <c r="M28" s="4">
+        <v>6</v>
+      </c>
       <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="O28" s="4">
+        <v>2</v>
+      </c>
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
@@ -5331,26 +5384,44 @@
       <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="7" t="str">
+      <c r="W28" s="7">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2</v>
       </c>
       <c r="X28" s="6"/>
     </row>
     <row r="29" spans="1:24" ht="38.1" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="B29" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="H29" s="5"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
+      <c r="I29" s="4">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4">
+        <v>1</v>
+      </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="4"/>
+      <c r="M29" s="4">
+        <v>10</v>
+      </c>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
       <c r="P29" s="4"/>
@@ -5360,28 +5431,46 @@
       <c r="T29" s="6"/>
       <c r="U29" s="6"/>
       <c r="V29" s="6"/>
-      <c r="W29" s="7" t="str">
+      <c r="W29" s="7">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="X29" s="6"/>
     </row>
     <row r="30" spans="1:24" ht="38.1" customHeight="1">
       <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="B30" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>153</v>
+      </c>
       <c r="H30" s="5"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
+      <c r="I30" s="4">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4">
+        <v>1</v>
+      </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
+      <c r="O30" s="4">
+        <v>5</v>
+      </c>
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
@@ -5389,9 +5478,9 @@
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
-      <c r="W30" s="7" t="str">
+      <c r="W30" s="7">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="X30" s="6"/>
     </row>
@@ -8999,7 +9088,7 @@
         <v>PACK-COMMON-FOOD-01</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>358</v>
+        <v>649</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>359</v>
@@ -9018,7 +9107,7 @@
         <v>廢棄超市</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J33" si="0">IF(A2="","",IFERROR(F2*G2/E2,0))</f>
@@ -9057,7 +9146,7 @@
         <v>廢棄超市</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="J3" s="21">
         <f t="shared" si="0"/>
@@ -9096,7 +9185,7 @@
         <v>廢棄超市</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="J4" s="21">
         <f t="shared" si="0"/>
@@ -9135,7 +9224,7 @@
         <v>住宅區</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
@@ -9211,7 +9300,7 @@
         <v>住宅區</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="J7" s="21">
         <f t="shared" si="0"/>
@@ -9250,7 +9339,7 @@
         <v>住宅區</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="0"/>
@@ -9363,7 +9452,7 @@
         <v>消防局</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="0"/>
@@ -9476,7 +9565,7 @@
         <v>五金行</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="0"/>
@@ -9533,7 +9622,7 @@
         <v>PACK-UNCOMMON-RESOURCE-01</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>359</v>
@@ -9626,7 +9715,7 @@
         <v>倉庫</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="J18" s="21">
         <f t="shared" si="0"/>
@@ -11261,7 +11350,7 @@
         <v/>
       </c>
       <c r="K98" s="22" t="str">
-        <f t="shared" ref="K98:K129" si="6">IF(A98="","",IFERROR(J98/SUMIF($A$2:$A$100,A98,$J$2:$J$100),0))</f>
+        <f t="shared" ref="K98:K100" si="6">IF(A98="","",IFERROR(J98/SUMIF($A$2:$A$100,A98,$J$2:$J$100),0))</f>
         <v/>
       </c>
     </row>
